--- a/03_Outputs/Bioenergetica_Norte/10_Seguridad/seguridad.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/10_Seguridad/seguridad.xlsx
@@ -19,20 +19,23 @@
     <sheet name="P6_cambio_municipio" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="irv" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="desaparecidos" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="_fig_01" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="_fig_02" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="_fig_03" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="_fig_04" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="_fig_05" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="_mapa10_homicidios" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="_mapa10_homicidios_dpto" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="reparacion_colectiva" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="reparacion_colectiva_sujetos" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="_fig_01" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_02" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_03" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_fig_04" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_fig_05" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_fig_06" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="_mapa10_homicidios" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="_mapa10_homicidios_dpto" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="73">
+  <numFmts count="80">
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
@@ -106,8 +109,15 @@
     <numFmt numFmtId="235" formatCode="#,##0"/>
     <numFmt numFmtId="236" formatCode="0.0%"/>
     <numFmt numFmtId="237" formatCode="0.0%"/>
+    <numFmt numFmtId="238" formatCode="#,##0"/>
+    <numFmt numFmtId="239" formatCode="#,##0"/>
+    <numFmt numFmtId="240" formatCode="#,##0"/>
+    <numFmt numFmtId="241" formatCode="#,##0"/>
+    <numFmt numFmtId="242" formatCode="0.0%"/>
+    <numFmt numFmtId="243" formatCode="0.0%"/>
+    <numFmt numFmtId="244" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,23 +127,307 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -153,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -164,73 +458,131 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="204" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="11" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="13" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="214" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="15" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="17" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="234" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="235" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="20" numFmtId="235" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="236" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="237" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="20" numFmtId="237" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="239" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="241" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="22" numFmtId="243" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="24" fontId="31" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,13 +911,13 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -822,46 +1174,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="5" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Muy seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>Seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="84" t="inlineStr">
         <is>
           <t>Inseguro (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="84" t="inlineStr">
         <is>
           <t>Muy inseguro (%)</t>
         </is>
@@ -878,19 +1231,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="66">
+      <c r="C2" s="89">
         <v>344</v>
       </c>
-      <c r="D2" s="62">
+      <c r="D2" s="85">
         <v>0.0709119776858088</v>
       </c>
-      <c r="E2" s="63">
+      <c r="E2" s="86">
         <v>0.568952987569571</v>
       </c>
-      <c r="F2" s="64">
+      <c r="F2" s="87">
         <v>0.258066916691138</v>
       </c>
-      <c r="G2" s="65">
+      <c r="G2" s="88">
         <v>0.102068118053482</v>
       </c>
     </row>
@@ -905,19 +1258,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="66">
+      <c r="C3" s="89">
         <v>344</v>
       </c>
-      <c r="D3" s="62">
+      <c r="D3" s="85">
         <v>0.110026323719227</v>
       </c>
-      <c r="E3" s="63">
+      <c r="E3" s="86">
         <v>0.638375585902372</v>
       </c>
-      <c r="F3" s="64">
+      <c r="F3" s="87">
         <v>0.208039147100188</v>
       </c>
-      <c r="G3" s="65">
+      <c r="G3" s="88">
         <v>0.0435589432782132</v>
       </c>
     </row>
@@ -932,19 +1285,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="66">
+      <c r="C4" s="89">
         <v>336</v>
       </c>
-      <c r="D4" s="62">
+      <c r="D4" s="85">
         <v>0.0968497273682837</v>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="86">
         <v>0.694391114553894</v>
       </c>
-      <c r="F4" s="64">
+      <c r="F4" s="87">
         <v>0.168463820658172</v>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="88">
         <v>0.0402953374196502</v>
       </c>
     </row>
@@ -959,19 +1312,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="66">
+      <c r="C5" s="89">
         <v>216</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="85">
         <v>0.0506475683150735</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="86">
         <v>0.696174020100695</v>
       </c>
-      <c r="F5" s="64">
+      <c r="F5" s="87">
         <v>0.206430029843191</v>
       </c>
-      <c r="G5" s="65">
+      <c r="G5" s="88">
         <v>0.0467483817410409</v>
       </c>
     </row>
@@ -986,19 +1339,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="66">
+      <c r="C6" s="89">
         <v>272</v>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="85">
         <v>0.0773599396187067</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="86">
         <v>0.761660428482399</v>
       </c>
-      <c r="F6" s="64">
+      <c r="F6" s="87">
         <v>0.138086208991511</v>
       </c>
-      <c r="G6" s="65">
+      <c r="G6" s="88">
         <v>0.0228934229073834</v>
       </c>
     </row>
@@ -1013,19 +1366,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="66">
+      <c r="C7" s="89">
         <v>272</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="85">
         <v>0.122530769984082</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="86">
         <v>0.646896535699251</v>
       </c>
-      <c r="F7" s="64">
+      <c r="F7" s="87">
         <v>0.184575163012394</v>
       </c>
-      <c r="G7" s="65">
+      <c r="G7" s="88">
         <v>0.0459975313042729</v>
       </c>
     </row>
@@ -1040,19 +1393,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="66">
+      <c r="C8" s="89">
         <v>240</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="85">
         <v>0.0850803388362212</v>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="86">
         <v>0.675680791164399</v>
       </c>
-      <c r="F8" s="64">
+      <c r="F8" s="87">
         <v>0.205778697238382</v>
       </c>
-      <c r="G8" s="65">
+      <c r="G8" s="88">
         <v>0.0334601727609976</v>
       </c>
     </row>
@@ -1067,19 +1420,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="66">
+      <c r="C9" s="89">
         <v>249</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="85">
         <v>0.0770187542355022</v>
       </c>
-      <c r="E9" s="63">
+      <c r="E9" s="86">
         <v>0.714033165981444</v>
       </c>
-      <c r="F9" s="64">
+      <c r="F9" s="87">
         <v>0.176907170989814</v>
       </c>
-      <c r="G9" s="65">
+      <c r="G9" s="88">
         <v>0.0320409087932396</v>
       </c>
     </row>
@@ -1095,45 +1448,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="91" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="91" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="91" t="inlineStr">
         <is>
           <t>Más seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="91" t="inlineStr">
         <is>
           <t>Menos seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="91" t="inlineStr">
         <is>
           <t>Igual (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="91" t="inlineStr">
         <is>
           <t>No sabe/No responde (%)</t>
         </is>
@@ -1150,19 +1505,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="71">
+      <c r="C2" s="96">
         <v>344</v>
       </c>
-      <c r="D2" s="67">
+      <c r="D2" s="92">
         <v>0.176314482754761</v>
       </c>
-      <c r="E2" s="68">
+      <c r="E2" s="93">
         <v>0.193762546944013</v>
       </c>
-      <c r="F2" s="69">
+      <c r="F2" s="94">
         <v>0.617257757966248</v>
       </c>
-      <c r="G2" s="70">
+      <c r="G2" s="95">
         <v>0.0126652123349779</v>
       </c>
     </row>
@@ -1177,19 +1532,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="71">
+      <c r="C3" s="96">
         <v>344</v>
       </c>
-      <c r="D3" s="67">
+      <c r="D3" s="92">
         <v>0.278560355464205</v>
       </c>
-      <c r="E3" s="68">
+      <c r="E3" s="93">
         <v>0.167363939224072</v>
       </c>
-      <c r="F3" s="69">
+      <c r="F3" s="94">
         <v>0.514827646802668</v>
       </c>
-      <c r="G3" s="70">
+      <c r="G3" s="95">
         <v>0.0392480585090547</v>
       </c>
     </row>
@@ -1204,19 +1559,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="71">
+      <c r="C4" s="96">
         <v>336</v>
       </c>
-      <c r="D4" s="67">
+      <c r="D4" s="92">
         <v>0.233565166922982</v>
       </c>
-      <c r="E4" s="68">
+      <c r="E4" s="93">
         <v>0.153541409122006</v>
       </c>
-      <c r="F4" s="69">
+      <c r="F4" s="94">
         <v>0.604812101060503</v>
       </c>
-      <c r="G4" s="70">
+      <c r="G4" s="95">
         <v>0.00808132289450913</v>
       </c>
     </row>
@@ -1231,19 +1586,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="71">
+      <c r="C5" s="96">
         <v>216</v>
       </c>
-      <c r="D5" s="67">
+      <c r="D5" s="92">
         <v>0.140066275502638</v>
       </c>
-      <c r="E5" s="68">
+      <c r="E5" s="93">
         <v>0.132002665109143</v>
       </c>
-      <c r="F5" s="69">
+      <c r="F5" s="94">
         <v>0.726429348817849</v>
       </c>
-      <c r="G5" s="70">
+      <c r="G5" s="95">
         <v>0.00150171057037049</v>
       </c>
     </row>
@@ -1258,19 +1613,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="71">
+      <c r="C6" s="96">
         <v>272</v>
       </c>
-      <c r="D6" s="67">
+      <c r="D6" s="92">
         <v>0.134515076855215</v>
       </c>
-      <c r="E6" s="68">
+      <c r="E6" s="93">
         <v>0.119725843446203</v>
       </c>
-      <c r="F6" s="69">
+      <c r="F6" s="94">
         <v>0.744791852855714</v>
       </c>
-      <c r="G6" s="70">
+      <c r="G6" s="95">
         <v>0.000967226842867905</v>
       </c>
     </row>
@@ -1285,19 +1640,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="96">
         <v>272</v>
       </c>
-      <c r="D7" s="67">
+      <c r="D7" s="92">
         <v>0.136338371062558</v>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="93">
         <v>0.111841445233229</v>
       </c>
-      <c r="F7" s="69">
+      <c r="F7" s="94">
         <v>0.751820183704213</v>
       </c>
-      <c r="G7" s="70">
+      <c r="G7" s="95">
         <v>0</v>
       </c>
     </row>
@@ -1312,19 +1667,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="71">
+      <c r="C8" s="96">
         <v>240</v>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="92">
         <v>0.209618412700499</v>
       </c>
-      <c r="E8" s="68">
+      <c r="E8" s="93">
         <v>0.131500879779058</v>
       </c>
-      <c r="F8" s="69">
+      <c r="F8" s="94">
         <v>0.651516195074017</v>
       </c>
-      <c r="G8" s="70">
+      <c r="G8" s="95">
         <v>0.00736451244642682</v>
       </c>
     </row>
@@ -1339,19 +1694,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="71">
+      <c r="C9" s="96">
         <v>249</v>
       </c>
-      <c r="D9" s="67">
+      <c r="D9" s="92">
         <v>0.181301163183468</v>
       </c>
-      <c r="E9" s="68">
+      <c r="E9" s="93">
         <v>0.117584831864874</v>
       </c>
-      <c r="F9" s="69">
+      <c r="F9" s="94">
         <v>0.69399686143753</v>
       </c>
-      <c r="G9" s="70">
+      <c r="G9" s="95">
         <v>0.00711714351412855</v>
       </c>
     </row>
@@ -1367,41 +1722,41 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="98" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="98" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="98" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="98" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="98" t="inlineStr">
         <is>
           <t>Índice de Riesgo de Victimización</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="98" t="inlineStr">
         <is>
           <t>Categoría de riesgo</t>
         </is>
@@ -1426,7 +1781,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="72">
+      <c r="E2" s="99">
         <v>0.38995486</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -1454,7 +1809,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="72">
+      <c r="E3" s="99">
         <v>0.73631903</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -1482,7 +1837,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="72">
+      <c r="E4" s="99">
         <v>0.84158239</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -1510,7 +1865,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="99">
         <v>0.57664494</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -1538,7 +1893,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="72">
+      <c r="E6" s="99">
         <v>0.12707096</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -1566,7 +1921,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="72">
+      <c r="E7" s="99">
         <v>0.28039983</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -1594,7 +1949,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="72">
+      <c r="E8" s="99">
         <v>0.0880462</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -1622,7 +1977,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="72">
+      <c r="E9" s="99">
         <v>0.83367775</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -1650,7 +2005,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="72">
+      <c r="E10" s="99">
         <v>0.4211108</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -1678,7 +2033,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="72">
+      <c r="E11" s="99">
         <v>0.19282387</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -1706,7 +2061,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="72">
+      <c r="E12" s="99">
         <v>0.37846318</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -1734,7 +2089,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="72">
+      <c r="E13" s="99">
         <v>0.75531776</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -1762,7 +2117,7 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="72">
+      <c r="E14" s="99">
         <v>0.4689614</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -1783,41 +2138,41 @@
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="101" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="101" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="101" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="101" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="101" t="inlineStr">
         <is>
           <t>Personas dadas por desaparecidas</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="101" t="inlineStr">
         <is>
           <t>Proporción dentro de la provincia</t>
         </is>
@@ -1842,10 +2197,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="73">
+      <c r="E2" s="103">
         <v>517</v>
       </c>
-      <c r="F2" s="75">
+      <c r="F2" s="105">
         <v>0.362298528381219</v>
       </c>
     </row>
@@ -1868,10 +2223,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="73">
+      <c r="E3" s="103">
         <v>265</v>
       </c>
-      <c r="F3" s="75">
+      <c r="F3" s="105">
         <v>0.185704274702172</v>
       </c>
     </row>
@@ -1894,10 +2249,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="73">
+      <c r="E4" s="103">
         <v>161</v>
       </c>
-      <c r="F4" s="75">
+      <c r="F4" s="105">
         <v>0.112824106517169</v>
       </c>
     </row>
@@ -1920,10 +2275,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="73">
+      <c r="E5" s="103">
         <v>158</v>
       </c>
-      <c r="F5" s="75">
+      <c r="F5" s="105">
         <v>0.110721793973371</v>
       </c>
     </row>
@@ -1946,10 +2301,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="73">
+      <c r="E6" s="103">
         <v>65</v>
       </c>
-      <c r="F6" s="75">
+      <c r="F6" s="105">
         <v>0.0455501051156272</v>
       </c>
     </row>
@@ -1972,10 +2327,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="73">
+      <c r="E7" s="103">
         <v>61</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="105">
         <v>0.0427470217238963</v>
       </c>
     </row>
@@ -1998,10 +2353,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="73">
+      <c r="E8" s="103">
         <v>42</v>
       </c>
-      <c r="F8" s="75">
+      <c r="F8" s="105">
         <v>0.0294323756131745</v>
       </c>
     </row>
@@ -2024,10 +2379,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="73">
+      <c r="E9" s="103">
         <v>38</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="105">
         <v>0.0266292922214436</v>
       </c>
     </row>
@@ -2050,10 +2405,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="73">
+      <c r="E10" s="103">
         <v>35</v>
       </c>
-      <c r="F10" s="75">
+      <c r="F10" s="105">
         <v>0.0245269796776454</v>
       </c>
     </row>
@@ -2076,10 +2431,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="73">
+      <c r="E11" s="103">
         <v>33</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="105">
         <v>0.02312543798178</v>
       </c>
     </row>
@@ -2102,10 +2457,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="73">
+      <c r="E12" s="103">
         <v>21</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="105">
         <v>0.0147161878065872</v>
       </c>
     </row>
@@ -2128,10 +2483,10 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="73">
+      <c r="E13" s="103">
         <v>16</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="105">
         <v>0.0112123335669236</v>
       </c>
     </row>
@@ -2154,38 +2509,38 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="73">
+      <c r="E14" s="103">
         <v>15</v>
       </c>
-      <c r="F14" s="75">
+      <c r="F14" s="105">
         <v>0.0105115627189909</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="102" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="102" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="102" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E15" s="74">
+      <c r="D15" s="102" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E15" s="104">
         <v>1427</v>
       </c>
-      <c r="F15" s="76">
+      <c r="F15" s="106">
         <v>1</v>
       </c>
     </row>
@@ -2198,299 +2553,483 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="63.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="62.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>periodo</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ambito</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>n_resp</t>
+      <c r="A1" s="108" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="108" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="108" t="inlineStr">
+        <is>
+          <t>Subregión</t>
+        </is>
+      </c>
+      <c r="D1" s="108" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="E1" s="108" t="inlineStr">
+        <is>
+          <t>Sujetos de reparación colectiva reconocidos</t>
+        </is>
+      </c>
+      <c r="F1" s="108" t="inlineStr">
+        <is>
+          <t>Sujetos con Plan Integral de Reparación Colectiva implementado</t>
+        </is>
+      </c>
+      <c r="G1" s="108" t="inlineStr">
+        <is>
+          <t>% de avance del PIRC, promedio (solo sujetos con plan activo)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>2018</v>
+        <v>5361</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>0.247309549143037</v>
-      </c>
-      <c r="D2">
-        <v>344</v>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E2" s="110">
+        <v>4</v>
+      </c>
+      <c r="F2" s="112">
+        <v>0</v>
+      </c>
+      <c r="G2" s="114">
+        <v>0.36444444444</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2019 (1)</t>
-        </is>
+      <c r="A3">
+        <v>5887</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>0.181036257130808</v>
-      </c>
-      <c r="D3">
-        <v>344</v>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E3" s="110">
+        <v>3</v>
+      </c>
+      <c r="F3" s="112">
+        <v>0</v>
+      </c>
+      <c r="G3" s="114">
+        <v>0.16041666667</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2019 (2)</t>
-        </is>
+      <c r="A4">
+        <v>5038</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>0.145889472818591</v>
-      </c>
-      <c r="D4">
-        <v>336</v>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E4" s="110">
+        <v>0</v>
+      </c>
+      <c r="F4" s="112">
+        <v>0</v>
+      </c>
+      <c r="G4" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2021</v>
+        <v>5040</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>0.186356719168937</v>
-      </c>
-      <c r="D5">
-        <v>216</v>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NORDESTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E5" s="110">
+        <v>0</v>
+      </c>
+      <c r="F5" s="112">
+        <v>0</v>
+      </c>
+      <c r="G5" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2022</v>
+        <v>5107</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0.148855733765853</v>
-      </c>
-      <c r="D6">
-        <v>272</v>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E6" s="110">
+        <v>0</v>
+      </c>
+      <c r="F6" s="112">
+        <v>0</v>
+      </c>
+      <c r="G6" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>2023</v>
+        <v>5134</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.157717210185655</v>
-      </c>
-      <c r="D7">
-        <v>272</v>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E7" s="110">
+        <v>0</v>
+      </c>
+      <c r="F7" s="112">
+        <v>0</v>
+      </c>
+      <c r="G7" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>2024</v>
+        <v>5150</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.155654086292368</v>
-      </c>
-      <c r="D8">
-        <v>240</v>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E8" s="110">
+        <v>0</v>
+      </c>
+      <c r="F8" s="112">
+        <v>0</v>
+      </c>
+      <c r="G8" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2025</v>
+        <v>5315</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>En su barrio o vereda</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.10353955335921</v>
-      </c>
-      <c r="D9">
-        <v>249</v>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E9" s="110">
+        <v>0</v>
+      </c>
+      <c r="F9" s="112">
+        <v>0</v>
+      </c>
+      <c r="G9" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2018</v>
+        <v>5310</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>0.36013503474462</v>
-      </c>
-      <c r="D10">
-        <v>344</v>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E10" s="110">
+        <v>0</v>
+      </c>
+      <c r="F10" s="112">
+        <v>0</v>
+      </c>
+      <c r="G10" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2019 (1)</t>
-        </is>
+      <c r="A11">
+        <v>5647</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>0.251598090378401</v>
-      </c>
-      <c r="D11">
-        <v>344</v>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E11" s="110">
+        <v>0</v>
+      </c>
+      <c r="F11" s="112">
+        <v>0</v>
+      </c>
+      <c r="G11" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2019 (2)</t>
-        </is>
+      <c r="A12">
+        <v>5658</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>0.208759158077822</v>
-      </c>
-      <c r="D12">
-        <v>336</v>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E12" s="110">
+        <v>0</v>
+      </c>
+      <c r="F12" s="112">
+        <v>0</v>
+      </c>
+      <c r="G12" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>2021</v>
+        <v>5819</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>0.253178411584232</v>
-      </c>
-      <c r="D13">
-        <v>216</v>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E13" s="110">
+        <v>0</v>
+      </c>
+      <c r="F13" s="112">
+        <v>0</v>
+      </c>
+      <c r="G13" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>2022</v>
+        <v>5854</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>0.160979631898894</v>
-      </c>
-      <c r="D14">
-        <v>272</v>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E14" s="110">
+        <v>0</v>
+      </c>
+      <c r="F14" s="112">
+        <v>0</v>
+      </c>
+      <c r="G14" s="114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>2023</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>0.230572694316667</v>
-      </c>
-      <c r="D15">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>2024</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>0.239238869999379</v>
-      </c>
-      <c r="D16">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>En su municipio</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>0.208948079783054</v>
-      </c>
-      <c r="D17">
-        <v>249</v>
+      <c r="A15" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="109" t="inlineStr">
+        <is>
+          <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="C15" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="111">
+        <v>7</v>
+      </c>
+      <c r="F15" s="113">
+        <v>0</v>
+      </c>
+      <c r="G15" s="115">
+        <v>0.262430555555</v>
       </c>
     </row>
   </sheetData>
@@ -2502,243 +3041,416 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>n_solicitudes</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>pob</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>tasa_solicitudes</t>
+      <c r="A1" s="117" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="117" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="117" t="inlineStr">
+        <is>
+          <t>Subregión</t>
+        </is>
+      </c>
+      <c r="D1" s="117" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="E1" s="117" t="inlineStr">
+        <is>
+          <t>Sujeto de reparación colectiva</t>
+        </is>
+      </c>
+      <c r="F1" s="117" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="G1" s="117" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="H1" s="117" t="inlineStr">
+        <is>
+          <t>Fase del Plan Integral de Reparación Colectiva</t>
+        </is>
+      </c>
+      <c r="I1" s="117" t="inlineStr">
+        <is>
+          <t>% de avance del PIRC</t>
+        </is>
+      </c>
+      <c r="J1" s="117" t="inlineStr">
+        <is>
+          <t>Zona PDET</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>58</v>
-      </c>
-      <c r="C2">
-        <v>12511</v>
-      </c>
-      <c r="D2">
-        <v>4.63592039005675</v>
+      <c r="A2">
+        <v>5361</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RESGUARDO INDIGENA JAIDUKAMA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Étnico</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COMUNIDAD INDÍGENA (Decreto 4633 de 2011)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="I2" s="118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PDET Bajo Cauca-Nordeste Antioqueño</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>159</v>
-      </c>
-      <c r="C3">
-        <v>21035</v>
-      </c>
-      <c r="D3">
-        <v>7.55883052056097</v>
+      <c r="A3">
+        <v>5361</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>COMUNIDAD DE LA VEREDA SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="I3" s="118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PDET Bajo Cauca-Nordeste Antioqueño</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>117</v>
-      </c>
-      <c r="C4">
-        <v>7957</v>
-      </c>
-      <c r="D4">
-        <v>14.7040341837376</v>
+      <c r="A4">
+        <v>5361</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CORREGIMIENTO EL ARO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="I4" s="118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PDET Bajo Cauca-Nordeste Antioqueño</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>45</v>
-      </c>
-      <c r="C5">
-        <v>10005</v>
-      </c>
-      <c r="D5">
-        <v>4.49775112443778</v>
+      <c r="A5">
+        <v>5361</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CORREGIMIENTO LA GRANJA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I5" s="118">
+        <v>0.36444444444</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PDET Bajo Cauca-Nordeste Antioqueño</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>3942</v>
-      </c>
-      <c r="D6">
-        <v>1.01471334348047</v>
+      <c r="A6">
+        <v>5887</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMUNIDAD DEL CORREGIMIENTO LA LOMA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="I6" s="118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>7009</v>
-      </c>
-      <c r="D7">
-        <v>1.85475816806962</v>
+      <c r="A7">
+        <v>5887</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMUNIDAD DEL CORREGIMIENTO EL LLANO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="I7" s="118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>27</v>
-      </c>
-      <c r="C8">
-        <v>10373</v>
-      </c>
-      <c r="D8">
-        <v>2.60291140460812</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>445</v>
-      </c>
-      <c r="C9">
-        <v>29515</v>
-      </c>
-      <c r="D9">
-        <v>15.0770794511265</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>80</v>
-      </c>
-      <c r="C10">
-        <v>7402</v>
-      </c>
-      <c r="D10">
-        <v>10.8078897595245</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>4017</v>
-      </c>
-      <c r="D11">
-        <v>0.497883993029624</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>41</v>
-      </c>
-      <c r="C12">
-        <v>4824</v>
-      </c>
-      <c r="D12">
-        <v>8.49917081260365</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>155</v>
-      </c>
-      <c r="C13">
-        <v>15014</v>
-      </c>
-      <c r="D13">
-        <v>10.3236978819768</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A8">
+        <v>5887</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Yarumal</t>
         </is>
       </c>
-      <c r="B14">
-        <v>120</v>
-      </c>
-      <c r="C14">
-        <v>41884</v>
-      </c>
-      <c r="D14">
-        <v>2.86505586858944</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CORREGIMIENTO OCHALÍ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No Étnico</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>COMUNIDAD CAMPESINA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="I8" s="118">
+        <v>0.16041666667</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No PDET</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2750,198 +3462,299 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>desaparecidos</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>prop_desaparecidos</t>
+      <c r="A1" s="120" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="B1" s="120" t="inlineStr">
+        <is>
+          <t>ambito</t>
+        </is>
+      </c>
+      <c r="C1" s="120" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="D1" s="120" t="inlineStr">
+        <is>
+          <t>n_resp</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ituango</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>517</v>
+      <c r="A2">
+        <v>2018</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C2">
-        <v>0.362298528381219</v>
+        <v>0.247309549143037</v>
+      </c>
+      <c r="D2">
+        <v>344</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Valdivia</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>265</v>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C3">
-        <v>0.185704274702172</v>
+        <v>0.181036257130808</v>
+      </c>
+      <c r="D3">
+        <v>344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Yarumal</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>161</v>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C4">
-        <v>0.112824106517169</v>
+        <v>0.145889472818591</v>
+      </c>
+      <c r="D4">
+        <v>336</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Anorí</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>158</v>
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C5">
-        <v>0.110721793973371</v>
+        <v>0.186356719168937</v>
+      </c>
+      <c r="D5">
+        <v>216</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Campamento</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>65</v>
+      <c r="A6">
+        <v>2022</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C6">
-        <v>0.0455501051156272</v>
+        <v>0.148855733765853</v>
+      </c>
+      <c r="D6">
+        <v>272</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Briceño</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>61</v>
+      <c r="A7">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C7">
-        <v>0.0427470217238963</v>
+        <v>0.157717210185655</v>
+      </c>
+      <c r="D7">
+        <v>272</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Angostura</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>42</v>
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C8">
-        <v>0.0294323756131745</v>
+        <v>0.155654086292368</v>
+      </c>
+      <c r="D8">
+        <v>240</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>38</v>
+      <c r="A9">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>En su barrio o vereda</t>
+        </is>
       </c>
       <c r="C9">
-        <v>0.0266292922214436</v>
+        <v>0.10353955335921</v>
+      </c>
+      <c r="D9">
+        <v>249</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>San Andrés de Cuerquía</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>35</v>
+      <c r="A10">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
       </c>
       <c r="C10">
-        <v>0.0245269796776454</v>
+        <v>0.36013503474462</v>
+      </c>
+      <c r="D10">
+        <v>344</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>33</v>
+          <t>2019 (1)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
       </c>
       <c r="C11">
-        <v>0.02312543798178</v>
+        <v>0.251598090378401</v>
+      </c>
+      <c r="D11">
+        <v>344</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>San José de la Montaña</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>21</v>
+          <t>2019 (2)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
       </c>
       <c r="C12">
-        <v>0.0147161878065872</v>
+        <v>0.208759158077822</v>
+      </c>
+      <c r="D12">
+        <v>336</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Gómez Plata</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>16</v>
+      <c r="A13">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
       </c>
       <c r="C13">
-        <v>0.0112123335669236</v>
+        <v>0.253178411584232</v>
+      </c>
+      <c r="D13">
+        <v>216</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Carolina del Príncipe</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>15</v>
+      <c r="A14">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
       </c>
       <c r="C14">
-        <v>0.0105115627189909</v>
+        <v>0.160979631898894</v>
+      </c>
+      <c r="D14">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0.230572694316667</v>
+      </c>
+      <c r="D15">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0.239238869999379</v>
+      </c>
+      <c r="D16">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>En su municipio</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0.208948079783054</v>
+      </c>
+      <c r="D17">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -2953,22 +3766,34 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="122" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>victimas_ocurrencia</t>
+      <c r="B1" s="122" t="inlineStr">
+        <is>
+          <t>n_solicitudes</t>
+        </is>
+      </c>
+      <c r="C1" s="122" t="inlineStr">
+        <is>
+          <t>pob</t>
+        </is>
+      </c>
+      <c r="D1" s="122" t="inlineStr">
+        <is>
+          <t>tasa_solicitudes</t>
         </is>
       </c>
     </row>
@@ -2979,7 +3804,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>6757</v>
+        <v>58</v>
+      </c>
+      <c r="C2">
+        <v>12511</v>
+      </c>
+      <c r="D2">
+        <v>4.63592039005675</v>
       </c>
     </row>
     <row r="3">
@@ -2989,7 +3820,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>23517</v>
+        <v>159</v>
+      </c>
+      <c r="C3">
+        <v>21035</v>
+      </c>
+      <c r="D3">
+        <v>7.55883052056097</v>
       </c>
     </row>
     <row r="4">
@@ -2999,7 +3836,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>18213</v>
+        <v>117</v>
+      </c>
+      <c r="C4">
+        <v>7957</v>
+      </c>
+      <c r="D4">
+        <v>14.7040341837376</v>
       </c>
     </row>
     <row r="5">
@@ -3009,7 +3852,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>8670</v>
+        <v>45</v>
+      </c>
+      <c r="C5">
+        <v>10005</v>
+      </c>
+      <c r="D5">
+        <v>4.49775112443778</v>
       </c>
     </row>
     <row r="6">
@@ -3019,7 +3868,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>920</v>
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3942</v>
+      </c>
+      <c r="D6">
+        <v>1.01471334348047</v>
       </c>
     </row>
     <row r="7">
@@ -3029,7 +3884,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>3015</v>
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>7009</v>
+      </c>
+      <c r="D7">
+        <v>1.85475816806962</v>
       </c>
     </row>
     <row r="8">
@@ -3039,7 +3900,13 @@
         </is>
       </c>
       <c r="B8">
-        <v>1747</v>
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>10373</v>
+      </c>
+      <c r="D8">
+        <v>2.60291140460812</v>
       </c>
     </row>
     <row r="9">
@@ -3049,7 +3916,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>57522</v>
+        <v>445</v>
+      </c>
+      <c r="C9">
+        <v>29515</v>
+      </c>
+      <c r="D9">
+        <v>15.0770794511265</v>
       </c>
     </row>
     <row r="10">
@@ -3059,7 +3932,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>7404</v>
+        <v>80</v>
+      </c>
+      <c r="C10">
+        <v>7402</v>
+      </c>
+      <c r="D10">
+        <v>10.8078897595245</v>
       </c>
     </row>
     <row r="11">
@@ -3069,7 +3948,13 @@
         </is>
       </c>
       <c r="B11">
-        <v>1698</v>
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>4017</v>
+      </c>
+      <c r="D11">
+        <v>0.497883993029624</v>
       </c>
     </row>
     <row r="12">
@@ -3079,7 +3964,13 @@
         </is>
       </c>
       <c r="B12">
-        <v>7292</v>
+        <v>41</v>
+      </c>
+      <c r="C12">
+        <v>4824</v>
+      </c>
+      <c r="D12">
+        <v>8.49917081260365</v>
       </c>
     </row>
     <row r="13">
@@ -3089,7 +3980,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>25760</v>
+        <v>155</v>
+      </c>
+      <c r="C13">
+        <v>15014</v>
+      </c>
+      <c r="D13">
+        <v>10.3236978819768</v>
       </c>
     </row>
     <row r="14">
@@ -3099,7 +3996,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>19298</v>
+        <v>120</v>
+      </c>
+      <c r="C14">
+        <v>41884</v>
+      </c>
+      <c r="D14">
+        <v>2.86505586858944</v>
       </c>
     </row>
   </sheetData>
@@ -3111,237 +4014,198 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>hecho</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>victimas_ocurrencia</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>proporcion_pct</t>
+      <c r="A1" s="124" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="124" t="inlineStr">
+        <is>
+          <t>desaparecidos</t>
+        </is>
+      </c>
+      <c r="C1" s="124" t="inlineStr">
+        <is>
+          <t>prop_desaparecidos</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Desplazamiento forzado</t>
+          <t>Ituango</t>
         </is>
       </c>
       <c r="B2">
-        <v>130639</v>
+        <v>517</v>
       </c>
       <c r="C2">
-        <v>0.71853497824688</v>
+        <v>0.362298528381219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Homicidio</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="B3">
-        <v>19499</v>
+        <v>265</v>
       </c>
       <c r="C3">
-        <v>0.107247556555362</v>
+        <v>0.185704274702172</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amenaza</t>
+          <t>Yarumal</t>
         </is>
       </c>
       <c r="B4">
-        <v>19023</v>
+        <v>161</v>
       </c>
       <c r="C4">
-        <v>0.104629481940235</v>
+        <v>0.112824106517169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Desaparición forzada</t>
+          <t>Anorí</t>
         </is>
       </c>
       <c r="B5">
-        <v>3194</v>
+        <v>158</v>
       </c>
       <c r="C5">
-        <v>0.0175675006737692</v>
+        <v>0.110721793973371</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pérdida de bienes muebles/inmuebles</t>
+          <t>Campamento</t>
         </is>
       </c>
       <c r="B6">
-        <v>2015</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>0.011082815860252</v>
+        <v>0.0455501051156272</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Confinamiento</t>
+          <t>Briceño</t>
         </is>
       </c>
       <c r="B7">
-        <v>1554</v>
+        <v>61</v>
       </c>
       <c r="C7">
-        <v>0.0085472435964425</v>
+        <v>0.0427470217238963</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Acto terrorista/atentados/combates</t>
+          <t>Angostura</t>
         </is>
       </c>
       <c r="B8">
-        <v>1523</v>
+        <v>42</v>
       </c>
       <c r="C8">
-        <v>0.00837673873705401</v>
+        <v>0.0294323756131745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sin información</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="B9">
-        <v>1031</v>
+        <v>38</v>
       </c>
       <c r="C9">
-        <v>0.005670661613856</v>
+        <v>0.0266292922214436</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Minas antipersonal/MUSE</t>
+          <t>San Andrés de Cuerquía</t>
         </is>
       </c>
       <c r="B10">
-        <v>872</v>
+        <v>35</v>
       </c>
       <c r="C10">
-        <v>0.00479613668989566</v>
+        <v>0.0245269796776454</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Secuestro</t>
+          <t>Guadalupe</t>
         </is>
       </c>
       <c r="B11">
-        <v>818</v>
+        <v>33</v>
       </c>
       <c r="C11">
-        <v>0.00449912822515442</v>
+        <v>0.02312543798178</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lesiones personales físicas</t>
+          <t>San José de la Montaña</t>
         </is>
       </c>
       <c r="B12">
-        <v>684</v>
+        <v>21</v>
       </c>
       <c r="C12">
-        <v>0.00376210722005577</v>
+        <v>0.0147161878065872</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Delitos contra libertad/integridad sexual</t>
+          <t>Gómez Plata</t>
         </is>
       </c>
       <c r="B13">
-        <v>408</v>
+        <v>16</v>
       </c>
       <c r="C13">
-        <v>0.00224406395582274</v>
+        <v>0.0112123335669236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vinculación de NNA a grupos armados</t>
+          <t>Carolina del Príncipe</t>
         </is>
       </c>
       <c r="B14">
-        <v>224</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>0.00123203511300072</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Lesiones personales psicológicas</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>195</v>
-      </c>
-      <c r="C15">
-        <v>0.00107253056712116</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Tortura</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>117</v>
-      </c>
-      <c r="C16">
-        <v>0.000643518340272698</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Abandono o despojo de tierras</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>17</v>
-      </c>
-      <c r="C17">
-        <v>0.0000935026648259475</v>
+        <v>0.0105115627189909</v>
       </c>
     </row>
   </sheetData>
@@ -3353,198 +4217,153 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Código DANE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Municipio</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Homicidios por 100.000 hab.</t>
+      <c r="A1" s="126" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="126" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>5038</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Angostura</t>
         </is>
       </c>
-      <c r="C2">
-        <v>55.9507633282711</v>
+      <c r="B2">
+        <v>6757</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>5040</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Anorí</t>
         </is>
       </c>
-      <c r="C3">
-        <v>218.683147135726</v>
+      <c r="B3">
+        <v>23517</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>5107</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Briceño</t>
         </is>
       </c>
-      <c r="C4">
-        <v>226.21591051904</v>
+      <c r="B4">
+        <v>18213</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>5134</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Campamento</t>
         </is>
       </c>
-      <c r="C5">
-        <v>99.9500249875062</v>
+      <c r="B5">
+        <v>8670</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5150</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Carolina del Príncipe</t>
         </is>
       </c>
-      <c r="C6">
-        <v>76.103500761035</v>
+      <c r="B6">
+        <v>920</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>5315</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Guadalupe</t>
         </is>
       </c>
-      <c r="C7">
-        <v>42.8021115708375</v>
+      <c r="B7">
+        <v>3015</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>5310</v>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Gómez Plata</t>
         </is>
       </c>
-      <c r="C8">
-        <v>57.8424756579582</v>
+      <c r="B8">
+        <v>1747</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>5361</v>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Ituango</t>
         </is>
       </c>
-      <c r="C9">
-        <v>71.15026257835</v>
+      <c r="B9">
+        <v>57522</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>5647</v>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>San Andrés de Cuerquía</t>
         </is>
       </c>
-      <c r="C10">
-        <v>391.786003782761</v>
+      <c r="B10">
+        <v>7404</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>5658</v>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>San José de la Montaña</t>
         </is>
       </c>
-      <c r="C11">
-        <v>74.6825989544436</v>
+      <c r="B11">
+        <v>1698</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>5819</v>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Toledo</t>
         </is>
       </c>
-      <c r="C12">
-        <v>124.378109452736</v>
+      <c r="B12">
+        <v>7292</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>5854</v>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Valdivia</t>
         </is>
       </c>
-      <c r="C13">
-        <v>126.548554682297</v>
+      <c r="B13">
+        <v>25760</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>5887</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Yarumal</t>
         </is>
       </c>
-      <c r="C14">
-        <v>59.6886639289466</v>
+      <c r="B14">
+        <v>19298</v>
       </c>
     </row>
   </sheetData>
@@ -3559,59 +4378,59 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Hectáreas con permisos</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Hectáreas en tránsito</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Hectáreas ilícita</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Total EVOA (ha)</t>
         </is>
@@ -3636,19 +4455,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="13">
         <v>2018</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="15">
         <v>397.950798</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="17">
         <v>52.438321</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="19">
         <v>1237.886069</v>
       </c>
-      <c r="I2" s="18">
+      <c r="I2" s="21">
         <v>1688.275188</v>
       </c>
     </row>
@@ -3671,19 +4490,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="13">
         <v>2018</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="15">
         <v>0</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="17">
         <v>0</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="19">
         <v>1.639286</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="21">
         <v>1.639286</v>
       </c>
     </row>
@@ -3706,19 +4525,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="13">
         <v>2018</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="15">
         <v>0</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="17">
         <v>0</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="19">
         <v>23.377499</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="21">
         <v>23.377499</v>
       </c>
     </row>
@@ -3741,19 +4560,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="13">
         <v>2018</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="15">
         <v>0</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="17">
         <v>65.569309</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="19">
         <v>455.631976</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="21">
         <v>521.201285</v>
       </c>
     </row>
@@ -3776,19 +4595,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="13">
         <v>2019</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <v>525.431377</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="17">
         <v>49.007911</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="19">
         <v>1287.837522</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="21">
         <v>1862.27681</v>
       </c>
     </row>
@@ -3811,19 +4630,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="13">
         <v>2019</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="15">
         <v>0</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="17">
         <v>0.459309</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="19">
         <v>501.344919</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="21">
         <v>501.804228</v>
       </c>
     </row>
@@ -3846,19 +4665,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="13">
         <v>2020</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="15">
         <v>547.850897</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="17">
         <v>12.486491</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="19">
         <v>1438.754114</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="21">
         <v>1999.091502</v>
       </c>
     </row>
@@ -3881,352 +4700,352 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="13">
         <v>2020</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="15">
         <v>0</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="17">
         <v>129.510881</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="19">
         <v>296.684515</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="21">
         <v>426.195396</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E10" s="11">
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E10" s="14">
         <v>2018</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="16">
         <v>397.950798</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="18">
         <v>118.00763</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="20">
         <v>1718.53483</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="22">
         <v>2234.493258</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E11" s="11">
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E11" s="14">
         <v>2019</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="16">
         <v>525.431377</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="18">
         <v>49.46722</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="20">
         <v>1789.182441</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="22">
         <v>2364.081038</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E12" s="11">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E12" s="14">
         <v>2020</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="16">
         <v>547.850897</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="18">
         <v>141.997372</v>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="20">
         <v>1735.438629</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="22">
         <v>2425.286898</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="14">
         <v>2018</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="16">
         <v>0</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="18">
         <v>65.569309</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="20">
         <v>480.648761</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="22">
         <v>546.21807</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="14">
         <v>2019</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="16">
         <v>0</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="18">
         <v>0.459309</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="20">
         <v>501.344919</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="22">
         <v>501.804228</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="14">
         <v>2020</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="16">
         <v>0</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="18">
         <v>129.510881</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="20">
         <v>296.684515</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="22">
         <v>426.195396</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="14">
         <v>2018</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="16">
         <v>16186.547037</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="18">
         <v>1633.054856</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="20">
         <v>18627.422655</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="22">
         <v>36447.024548</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="14">
         <v>2019</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="16">
         <v>17799.238713</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="18">
         <v>1658.203768</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="20">
         <v>20744.042756</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="22">
         <v>40201.485237</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="14">
         <v>2020</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="16">
         <v>19240.998973</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="18">
         <v>1806.249069</v>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="20">
         <v>19842.333019</v>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="22">
         <v>40889.581061</v>
       </c>
     </row>
@@ -4239,26 +5058,512 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
+        <is>
+          <t>hecho</t>
+        </is>
+      </c>
+      <c r="B1" s="128" t="inlineStr">
+        <is>
+          <t>victimas_ocurrencia</t>
+        </is>
+      </c>
+      <c r="C1" s="128" t="inlineStr">
+        <is>
+          <t>proporcion_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Desplazamiento forzado</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>130639</v>
+      </c>
+      <c r="C2">
+        <v>0.71853497824688</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Homicidio</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>19499</v>
+      </c>
+      <c r="C3">
+        <v>0.107247556555362</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Amenaza</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>19023</v>
+      </c>
+      <c r="C4">
+        <v>0.104629481940235</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Desaparición forzada</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3194</v>
+      </c>
+      <c r="C5">
+        <v>0.0175675006737692</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pérdida de bienes muebles/inmuebles</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2015</v>
+      </c>
+      <c r="C6">
+        <v>0.011082815860252</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Confinamiento</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1554</v>
+      </c>
+      <c r="C7">
+        <v>0.0085472435964425</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Acto terrorista/atentados/combates</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1523</v>
+      </c>
+      <c r="C8">
+        <v>0.00837673873705401</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1031</v>
+      </c>
+      <c r="C9">
+        <v>0.005670661613856</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Minas antipersonal/MUSE</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>872</v>
+      </c>
+      <c r="C10">
+        <v>0.00479613668989566</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Secuestro</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>818</v>
+      </c>
+      <c r="C11">
+        <v>0.00449912822515442</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lesiones personales físicas</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>684</v>
+      </c>
+      <c r="C12">
+        <v>0.00376210722005577</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Delitos contra libertad/integridad sexual</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>408</v>
+      </c>
+      <c r="C13">
+        <v>0.00224406395582274</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Vinculación de NNA a grupos armados</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>224</v>
+      </c>
+      <c r="C14">
+        <v>0.00123203511300072</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lesiones personales psicológicas</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>195</v>
+      </c>
+      <c r="C15">
+        <v>0.00107253056712116</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tortura</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>117</v>
+      </c>
+      <c r="C16">
+        <v>0.000643518340272698</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Abandono o despojo de tierras</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>0.0000935026648259475</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="2.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="130" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="130" t="inlineStr">
+        <is>
+          <t>estado_fase</t>
+        </is>
+      </c>
+      <c r="C1" s="130" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ALISTAMIENTO</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CARACTERIZACIÓN DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO DEL DAÑO</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DISEÑO Y FORMULACIÓN</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IDENTIFICACIÓN</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IMPLEMENTADO</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="132" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="132" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="132" t="inlineStr">
         <is>
           <t>Homicidios por 100.000 hab.</t>
         </is>
@@ -4266,249 +5571,1375 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>5004</v>
+        <v>5038</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abriaquí</t>
+          <t>Angostura</t>
         </is>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>55.9507633282711</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>5138</v>
+        <v>5040</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cañasgordas</t>
+          <t>Anorí</t>
         </is>
       </c>
       <c r="C3">
-        <v>38.7847446670976</v>
+        <v>218.683147135726</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>5234</v>
+        <v>5107</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dabeiba</t>
+          <t>Briceño</t>
         </is>
       </c>
       <c r="C4">
-        <v>52.4024508223154</v>
+        <v>226.21591051904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>5284</v>
+        <v>5134</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Frontino</t>
+          <t>Campamento</t>
         </is>
       </c>
       <c r="C5">
-        <v>32.1425291578657</v>
+        <v>99.9500249875062</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5543</v>
+        <v>5150</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peque</t>
+          <t>Carolina del Príncipe</t>
         </is>
       </c>
       <c r="C6">
-        <v>11.3869278068777</v>
+        <v>76.103500761035</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5842</v>
+        <v>5315</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Uramita</t>
+          <t>Guadalupe</t>
         </is>
       </c>
       <c r="C7">
-        <v>13.4138162307176</v>
+        <v>42.8021115708375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>5038</v>
+        <v>5310</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Angostura</t>
+          <t>Gómez Plata</t>
         </is>
       </c>
       <c r="C8">
-        <v>55.9507633282711</v>
+        <v>57.8424756579582</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>5040</v>
+        <v>5361</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Anorí</t>
+          <t>Ituango</t>
         </is>
       </c>
       <c r="C9">
-        <v>218.683147135726</v>
+        <v>71.15026257835</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>5107</v>
+        <v>5647</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Briceño</t>
+          <t>San Andrés de Cuerquía</t>
         </is>
       </c>
       <c r="C10">
-        <v>226.21591051904</v>
+        <v>391.786003782761</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>5134</v>
+        <v>5658</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Campamento</t>
+          <t>San José de la Montaña</t>
         </is>
       </c>
       <c r="C11">
-        <v>99.9500249875062</v>
+        <v>74.6825989544436</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>5150</v>
+        <v>5819</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carolina del Príncipe</t>
+          <t>Toledo</t>
         </is>
       </c>
       <c r="C12">
-        <v>76.103500761035</v>
+        <v>124.378109452736</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>5315</v>
+        <v>5854</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guadalupe</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C13">
-        <v>42.8021115708375</v>
+        <v>126.548554682297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>5310</v>
+        <v>5887</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gómez Plata</t>
+          <t>Yarumal</t>
         </is>
       </c>
       <c r="C14">
-        <v>57.8424756579582</v>
+        <v>59.6886639289466</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C91"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="134" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="134" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="134" t="inlineStr">
+        <is>
+          <t>Homicidios por 100.000 hab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>5001</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>13.1706813513831</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>5002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Abejorral</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>28.3728188395517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>5004</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Abriaquí</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>5021</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alejandría</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>18.9214758751183</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5030</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Amagá</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>36.5207864142675</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5031</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Amalfi</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>113.581606663454</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5034</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Andes</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>147.684440231887</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5036</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Angelópolis</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>48.363694986297</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5038</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>55.9507633282711</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5040</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>218.683147135726</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>5042</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>31.6667253087506</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>5044</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anzá</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>52.0765525322224</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>5055</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Argelia</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>12.1728545343883</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>5361</v>
+        <v>5079</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ituango</t>
+          <t>Barbosa</t>
         </is>
       </c>
       <c r="C15">
-        <v>71.15026257835</v>
+        <v>17.3351193759357</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>5647</v>
+        <v>5086</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>San Andrés de Cuerquía</t>
+          <t>Belmira</t>
         </is>
       </c>
       <c r="C16">
-        <v>391.786003782761</v>
+        <v>81.2875955129247</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>5658</v>
+        <v>5088</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San José de la Montaña</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="C17">
-        <v>74.6825989544436</v>
+        <v>7.64226237548096</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>5819</v>
+        <v>5091</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>Betania</t>
         </is>
       </c>
       <c r="C18">
-        <v>124.378109452736</v>
+        <v>176.727746256162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>5854</v>
+        <v>5093</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Betulia</t>
         </is>
       </c>
       <c r="C19">
-        <v>126.548554682297</v>
+        <v>206.124852767962</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
+        <v>5101</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ciudad Bolívar</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>137.815979400138</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>5107</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>226.21591051904</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>5113</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>90.7852927825692</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>5125</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Caicedo</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>32.9416932030306</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>5129</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>12.3495599065924</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>5134</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>99.9500249875062</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>5138</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cañasgordas</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>38.7847446670976</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>5145</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Caramanta</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>22.2271615914648</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>5150</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>76.103500761035</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>5197</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cocorná</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>24.8617067561688</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>5206</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>39.1236306729264</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>5209</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Concordia</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>99.2645399990976</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>5212</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Copacabana</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>16.5049184657028</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>5234</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dabeiba</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>52.4024508223154</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>5237</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Donmatías</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>25.2614560703279</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>5240</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>5264</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Entrerríos</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>15.7035175879397</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>5266</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>3.02300887630981</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>5282</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fredonia</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>22.7264118783379</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>5284</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Frontino</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>32.1425291578657</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>5306</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>15.6152404747033</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>5308</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Girardota</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>4.88289197415322</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>5310</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>57.8424756579582</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>5313</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>19.0276852820854</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>5315</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>42.8021115708375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>5321</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Guatapé</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>30.9437854564208</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>5347</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>39.6982929734021</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>5353</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hispania</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>168.662506324844</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>5360</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Itagüí</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>3.61215918457148</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>5361</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>71.15026257835</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>5364</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jardín</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>71.2758374910905</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>5368</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Jericó</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>69.5603784084585</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>5380</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>9.62822997027284</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>5390</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>La Pintada</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>80.887450889762</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>5400</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>70.6655027642682</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>5440</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Marinilla</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>33.6066675628445</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>5467</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Montebello</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>45.8855919241358</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>5483</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>63.6363636363636</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>5501</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>5541</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Peñol</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>41.9691946111554</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>5543</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Peque</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>11.3869278068777</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>5576</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pueblorrico</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>99.41455870982</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>5604</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Remedios</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>118.106659398565</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>5628</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>80.7346856393178</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>5631</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sabaneta</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>2.81288677193114</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>5642</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Salgar</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>100.396301188904</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>5647</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>391.786003782761</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>5649</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>11.8077695123391</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>5652</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>33.0141961043249</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>5656</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>81.7661488143908</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>5658</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>74.6825989544436</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>5660</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>62.2966705890496</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>5664</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>San Pedro de los Milagros</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>31.4084443846188</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>5667</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>22.9739819654242</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>5674</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>San Vicente Ferrer</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>40.3616402970617</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>5679</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>33.9328130302002</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>5686</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>22.3541392414495</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>5736</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Segovia</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>66.0854535749689</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>5756</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sonsón</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>38.9105058365759</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>5789</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Támesis</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>5.99736116108912</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>5792</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tarso</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>76.2660158633313</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>5809</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Titiribí</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>60.6743520845974</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>5819</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>124.378109452736</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>5842</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Uramita</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>13.4138162307176</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>5847</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Urrao</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>96.9113417531574</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>5854</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>126.548554682297</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>5856</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>14.8942508191838</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>5858</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Vegachí</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>41.1184210526316</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>5861</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Venecia</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>40.2835965194973</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>5885</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Yalí</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>25.9100919808265</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
         <v>5887</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Yarumal</t>
         </is>
       </c>
-      <c r="C20">
+      <c r="C90">
         <v>59.6886639289466</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>5890</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Yolombó</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>31.9514338205927</v>
       </c>
     </row>
   </sheetData>
@@ -4523,47 +6954,47 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="24" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="24" t="inlineStr">
         <is>
           <t>Hurtos por 100.000 hab.</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>Homicidios por 100.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>Violencia intrafamiliar por 100.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>Delitos sexuales por 100.000 hab.</t>
         </is>
@@ -4583,16 +7014,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="26">
         <v>15.985932379506</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="28">
         <v>55.9507633282711</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="30">
         <v>103.908560466789</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="32">
         <v>31.9718647590121</v>
       </c>
     </row>
@@ -4610,16 +7041,16 @@
           <t>NORDESTE</t>
         </is>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="26">
         <v>33.2778702163062</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="28">
         <v>218.683147135726</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="30">
         <v>99.8336106489185</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="32">
         <v>71.3097218920846</v>
       </c>
     </row>
@@ -4637,16 +7068,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="26">
         <v>12.5675505843911</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="28">
         <v>226.21591051904</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="30">
         <v>188.513258765867</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="32">
         <v>62.8377529219555</v>
       </c>
     </row>
@@ -4664,16 +7095,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="26">
         <v>9.99500249875062</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="28">
         <v>99.9500249875062</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="30">
         <v>49.9750124937531</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="32">
         <v>79.960019990005</v>
       </c>
     </row>
@@ -4691,16 +7122,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="26">
         <v>101.471334348047</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="28">
         <v>76.103500761035</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="30">
         <v>304.41400304414</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="32">
         <v>50.7356671740233</v>
       </c>
     </row>
@@ -4718,16 +7149,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="26">
         <v>28.534741047225</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="28">
         <v>42.8021115708375</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="30">
         <v>99.8715936652875</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="32">
         <v>71.3368526180625</v>
       </c>
     </row>
@@ -4745,16 +7176,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="26">
         <v>48.2020630482985</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="28">
         <v>57.8424756579582</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="30">
         <v>96.4041260965969</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="32">
         <v>57.8424756579582</v>
       </c>
     </row>
@@ -4772,16 +7203,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="26">
         <v>10.1643232254786</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="28">
         <v>71.15026257835</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="30">
         <v>40.6572929019143</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="32">
         <v>166.017279349483</v>
       </c>
     </row>
@@ -4799,16 +7230,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="26">
         <v>54.0394487976223</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="28">
         <v>391.786003782761</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="30">
         <v>202.647932991084</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="32">
         <v>67.5493109970278</v>
       </c>
     </row>
@@ -4826,16 +7257,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="26">
         <v>49.7883993029624</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="28">
         <v>74.6825989544436</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="30">
         <v>199.15359721185</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="32">
         <v>49.7883993029624</v>
       </c>
     </row>
@@ -4853,16 +7284,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="26">
         <v>20.7296849087894</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="28">
         <v>124.378109452736</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="30">
         <v>248.756218905473</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="32">
         <v>41.4593698175788</v>
       </c>
     </row>
@@ -4880,16 +7311,16 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="26">
         <v>26.6418009857466</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="28">
         <v>126.548554682297</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="30">
         <v>0</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="32">
         <v>0</v>
       </c>
     </row>
@@ -4907,103 +7338,103 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="26">
         <v>121.764874415051</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="28">
         <v>59.6886639289466</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="30">
         <v>167.128259001051</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="32">
         <v>69.2388501575781</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="27">
         <v>49.5760393873085</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="29">
         <v>111.688548504741</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="31">
         <v>113.967906637491</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="33">
         <v>75.218818380744</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D16" s="21">
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D16" s="27">
         <v>80.5691467101584</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="29">
         <v>69.6180005553796</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="31">
         <v>123.591506603932</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="33">
         <v>75.093573632769</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="27">
         <v>506.74242087463</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="29">
         <v>25.3306260114209</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="31">
         <v>276.471875355423</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="33">
         <v>71.9216577862736</v>
       </c>
     </row>
@@ -5019,59 +7450,59 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="35" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="35" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="35" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="35" t="inlineStr">
         <is>
           <t>Víctimas por ocurrencia</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="35" t="inlineStr">
         <is>
           <t>Víctimas por declaración</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="35" t="inlineStr">
         <is>
           <t>Víctimas por ubicación</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="35" t="inlineStr">
         <is>
           <t>Sujetos de atención</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="35" t="inlineStr">
         <is>
           <t>Eventos</t>
         </is>
@@ -5096,19 +7527,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="37">
         <v>6757</v>
       </c>
-      <c r="F2" s="30">
+      <c r="F2" s="39">
         <v>3566</v>
       </c>
-      <c r="G2" s="32">
+      <c r="G2" s="41">
         <v>3409</v>
       </c>
-      <c r="H2" s="34">
+      <c r="H2" s="43">
         <v>2849</v>
       </c>
-      <c r="I2" s="36">
+      <c r="I2" s="45">
         <v>7406</v>
       </c>
     </row>
@@ -5131,19 +7562,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="37">
         <v>23517</v>
       </c>
-      <c r="F3" s="30">
+      <c r="F3" s="39">
         <v>10596</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="41">
         <v>9808</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="43">
         <v>8197</v>
       </c>
-      <c r="I3" s="36">
+      <c r="I3" s="45">
         <v>25749</v>
       </c>
     </row>
@@ -5166,19 +7597,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="37">
         <v>18213</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="39">
         <v>6233</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="41">
         <v>5643</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="43">
         <v>4569</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="45">
         <v>22817</v>
       </c>
     </row>
@@ -5201,19 +7632,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="37">
         <v>8670</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="39">
         <v>3846</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="41">
         <v>3299</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="43">
         <v>2788</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="45">
         <v>9335</v>
       </c>
     </row>
@@ -5236,19 +7667,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="37">
         <v>920</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="39">
         <v>637</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="41">
         <v>611</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="43">
         <v>523</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="45">
         <v>940</v>
       </c>
     </row>
@@ -5271,19 +7702,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="37">
         <v>3015</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="39">
         <v>936</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="41">
         <v>964</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="43">
         <v>786</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="45">
         <v>3129</v>
       </c>
     </row>
@@ -5306,19 +7737,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="37">
         <v>1747</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="39">
         <v>1174</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="41">
         <v>1253</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="43">
         <v>1059</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="45">
         <v>1815</v>
       </c>
     </row>
@@ -5341,19 +7772,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="37">
         <v>57522</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="39">
         <v>23441</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="41">
         <v>16998</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="43">
         <v>14460</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="45">
         <v>75130</v>
       </c>
     </row>
@@ -5376,19 +7807,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="37">
         <v>7404</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="39">
         <v>3730</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="41">
         <v>3109</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="43">
         <v>2592</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="45">
         <v>7986</v>
       </c>
     </row>
@@ -5411,19 +7842,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="37">
         <v>1698</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="39">
         <v>1107</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="41">
         <v>905</v>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="43">
         <v>769</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="45">
         <v>1741</v>
       </c>
     </row>
@@ -5446,19 +7877,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="37">
         <v>7292</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="39">
         <v>3579</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="41">
         <v>2726</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="43">
         <v>2226</v>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="45">
         <v>7883</v>
       </c>
     </row>
@@ -5481,19 +7912,19 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="37">
         <v>25760</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="39">
         <v>9813</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="41">
         <v>10428</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="43">
         <v>8525</v>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="45">
         <v>27981</v>
       </c>
     </row>
@@ -5516,56 +7947,56 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="37">
         <v>19298</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="39">
         <v>16268</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="41">
         <v>14769</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="43">
         <v>12203</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="45">
         <v>20395</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E15" s="29">
+      <c r="D15" s="36" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E15" s="38">
         <v>181813</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="40">
         <v>84926</v>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="42">
         <v>73922</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="44">
         <v>61546</v>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="46">
         <v>212307</v>
       </c>
     </row>
@@ -5581,23 +8012,23 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="87.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="88.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>Hecho victimizante</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="48" t="inlineStr">
         <is>
           <t>Víctimas por ocurrencia</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="48" t="inlineStr">
         <is>
           <t>Proporción sobre el total (%)</t>
         </is>
@@ -5609,10 +8040,10 @@
           <t>Desplazamiento forzado</t>
         </is>
       </c>
-      <c r="B2" s="38">
+      <c r="B2" s="49">
         <v>130639</v>
       </c>
-      <c r="C2" s="39">
+      <c r="C2" s="50">
         <v>0.71853497824688</v>
       </c>
     </row>
@@ -5622,10 +8053,10 @@
           <t>Homicidio (Conflicto)</t>
         </is>
       </c>
-      <c r="B3" s="38">
+      <c r="B3" s="49">
         <v>19499</v>
       </c>
-      <c r="C3" s="39">
+      <c r="C3" s="50">
         <v>0.107247556555362</v>
       </c>
     </row>
@@ -5635,10 +8066,10 @@
           <t>Amenaza (Conflicto)</t>
         </is>
       </c>
-      <c r="B4" s="38">
+      <c r="B4" s="49">
         <v>19023</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="50">
         <v>0.104629481940235</v>
       </c>
     </row>
@@ -5648,10 +8079,10 @@
           <t>Desaparición forzada</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="49">
         <v>3194</v>
       </c>
-      <c r="C5" s="39">
+      <c r="C5" s="50">
         <v>0.0175675006737692</v>
       </c>
     </row>
@@ -5661,10 +8092,10 @@
           <t>Perdida de Bienes Muebles o Inmuebles</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="49">
         <v>2015</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="50">
         <v>0.011082815860252</v>
       </c>
     </row>
@@ -5674,10 +8105,10 @@
           <t>Confinamiento (Conflicto)</t>
         </is>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="49">
         <v>1554</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="50">
         <v>0.0085472435964425</v>
       </c>
     </row>
@@ -5687,10 +8118,10 @@
           <t>Acto terrorista / Atentados / Combates / Enfrentamientos / Hostigamientos</t>
         </is>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="49">
         <v>1523</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="50">
         <v>0.00837673873705401</v>
       </c>
     </row>
@@ -5700,10 +8131,10 @@
           <t>Sin informacion (Conflicto)</t>
         </is>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="49">
         <v>1031</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="50">
         <v>0.005670661613856</v>
       </c>
     </row>
@@ -5713,10 +8144,10 @@
           <t>Minas Antipersonal, Munición sin Explotar y Artefacto Explosivo improvisado</t>
         </is>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="49">
         <v>872</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="50">
         <v>0.00479613668989566</v>
       </c>
     </row>
@@ -5726,10 +8157,10 @@
           <t>Secuestro (Conflicto)</t>
         </is>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="49">
         <v>818</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="50">
         <v>0.00449912822515442</v>
       </c>
     </row>
@@ -5739,10 +8170,10 @@
           <t>Lesiones Personales Fisicas</t>
         </is>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="49">
         <v>684</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="50">
         <v>0.00376210722005577</v>
       </c>
     </row>
@@ -5752,10 +8183,10 @@
           <t>Delitos contra la libertad y la integridad sexual en desarrollo del conflicto armado</t>
         </is>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="49">
         <v>408</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="50">
         <v>0.00224406395582274</v>
       </c>
     </row>
@@ -5765,10 +8196,10 @@
           <t>Vinculación de Niños Niñas y Adolescentes a Actividades Relacionadas con grupos armados</t>
         </is>
       </c>
-      <c r="B14" s="38">
+      <c r="B14" s="49">
         <v>224</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="50">
         <v>0.00123203511300072</v>
       </c>
     </row>
@@ -5778,10 +8209,10 @@
           <t>Lesiones Personales Psicologicas</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="49">
         <v>195</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="50">
         <v>0.00107253056712116</v>
       </c>
     </row>
@@ -5791,10 +8222,10 @@
           <t>Tortura (Conflicto)</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="49">
         <v>117</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="50">
         <v>0.000643518340272698</v>
       </c>
     </row>
@@ -5804,10 +8235,10 @@
           <t>Abandono o Despojo Forzado de Tierras</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="49">
         <v>17</v>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="50">
         <v>0.0000935026648259475</v>
       </c>
     </row>
@@ -5817,10 +8248,10 @@
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="49">
         <v>181813</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="50">
         <v>1</v>
       </c>
     </row>
@@ -5836,47 +8267,47 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Número de solicitudes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Número de predios</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>Número de titulares</t>
         </is>
@@ -5901,13 +8332,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="40">
+      <c r="E2" s="54">
         <v>58</v>
       </c>
-      <c r="F2" s="42">
+      <c r="F2" s="56">
         <v>47</v>
       </c>
-      <c r="G2" s="44">
+      <c r="G2" s="58">
         <v>53</v>
       </c>
     </row>
@@ -5930,13 +8361,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="40">
+      <c r="E3" s="54">
         <v>159</v>
       </c>
-      <c r="F3" s="42">
+      <c r="F3" s="56">
         <v>143</v>
       </c>
-      <c r="G3" s="44">
+      <c r="G3" s="58">
         <v>138</v>
       </c>
     </row>
@@ -5959,13 +8390,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="54">
         <v>117</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="56">
         <v>112</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="58">
         <v>112</v>
       </c>
     </row>
@@ -5988,13 +8419,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="54">
         <v>45</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="56">
         <v>40</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="58">
         <v>43</v>
       </c>
     </row>
@@ -6017,13 +8448,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="54">
         <v>4</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="56">
         <v>3</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="58">
         <v>4</v>
       </c>
     </row>
@@ -6046,13 +8477,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="54">
         <v>13</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="56">
         <v>12</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="58">
         <v>11</v>
       </c>
     </row>
@@ -6075,13 +8506,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="54">
         <v>27</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="56">
         <v>25</v>
       </c>
-      <c r="G8" s="44">
+      <c r="G8" s="58">
         <v>26</v>
       </c>
     </row>
@@ -6104,13 +8535,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="54">
         <v>445</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="56">
         <v>401</v>
       </c>
-      <c r="G9" s="44">
+      <c r="G9" s="58">
         <v>372</v>
       </c>
     </row>
@@ -6133,13 +8564,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="54">
         <v>80</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="56">
         <v>65</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="58">
         <v>69</v>
       </c>
     </row>
@@ -6162,13 +8593,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="54">
         <v>2</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="56">
         <v>2</v>
       </c>
-      <c r="G11" s="44">
+      <c r="G11" s="58">
         <v>2</v>
       </c>
     </row>
@@ -6191,13 +8622,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="54">
         <v>41</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="56">
         <v>35</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="58">
         <v>33</v>
       </c>
     </row>
@@ -6220,13 +8651,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="54">
         <v>155</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="56">
         <v>136</v>
       </c>
-      <c r="G13" s="44">
+      <c r="G13" s="58">
         <v>137</v>
       </c>
     </row>
@@ -6249,106 +8680,106 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="54">
         <v>120</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="56">
         <v>107</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G14" s="58">
         <v>102</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="53" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E15" s="41">
+      <c r="D15" s="53" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E15" s="55">
         <v>1266</v>
       </c>
-      <c r="F15" s="43">
+      <c r="F15" s="57">
         <v>1128</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="59">
         <v>1102</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="53" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="C16" s="53" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D16" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="55">
         <v>1184</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="57">
         <v>1056</v>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="59">
         <v>1022</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="53" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="53" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="53" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="55">
         <v>27352</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="57">
         <v>24834</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="59">
         <v>23637</v>
       </c>
     </row>
@@ -6364,47 +8795,47 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="61" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="61" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="61" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>Número de solicitudes</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="61" t="inlineStr">
         <is>
           <t>Población (2025)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="61" t="inlineStr">
         <is>
           <t>Tasa de solicitudes (por 1.000 hab.)</t>
         </is>
@@ -6429,13 +8860,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E2" s="46">
+      <c r="E2" s="63">
         <v>58</v>
       </c>
-      <c r="F2" s="48">
+      <c r="F2" s="65">
         <v>12511</v>
       </c>
-      <c r="G2" s="50">
+      <c r="G2" s="67">
         <v>4.63592039005675</v>
       </c>
     </row>
@@ -6458,13 +8889,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="63">
         <v>159</v>
       </c>
-      <c r="F3" s="48">
+      <c r="F3" s="65">
         <v>21035</v>
       </c>
-      <c r="G3" s="50">
+      <c r="G3" s="67">
         <v>7.55883052056097</v>
       </c>
     </row>
@@ -6487,13 +8918,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="63">
         <v>117</v>
       </c>
-      <c r="F4" s="48">
+      <c r="F4" s="65">
         <v>7957</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="67">
         <v>14.7040341837376</v>
       </c>
     </row>
@@ -6516,13 +8947,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="63">
         <v>45</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="65">
         <v>10005</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="67">
         <v>4.49775112443778</v>
       </c>
     </row>
@@ -6545,13 +8976,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="63">
         <v>4</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="65">
         <v>3942</v>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="67">
         <v>1.01471334348047</v>
       </c>
     </row>
@@ -6574,13 +9005,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="63">
         <v>13</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="65">
         <v>7009</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="67">
         <v>1.85475816806962</v>
       </c>
     </row>
@@ -6603,13 +9034,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="63">
         <v>27</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="65">
         <v>10373</v>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="67">
         <v>2.60291140460812</v>
       </c>
     </row>
@@ -6632,13 +9063,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="63">
         <v>445</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="65">
         <v>29515</v>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="67">
         <v>15.0770794511265</v>
       </c>
     </row>
@@ -6661,13 +9092,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="63">
         <v>80</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="65">
         <v>7402</v>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="67">
         <v>10.8078897595245</v>
       </c>
     </row>
@@ -6690,13 +9121,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="63">
         <v>2</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="65">
         <v>4017</v>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="67">
         <v>0.497883993029624</v>
       </c>
     </row>
@@ -6719,13 +9150,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="63">
         <v>41</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="65">
         <v>4824</v>
       </c>
-      <c r="G12" s="50">
+      <c r="G12" s="67">
         <v>8.49917081260365</v>
       </c>
     </row>
@@ -6748,13 +9179,13 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="63">
         <v>155</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="65">
         <v>15014</v>
       </c>
-      <c r="G13" s="50">
+      <c r="G13" s="67">
         <v>10.3236978819768</v>
       </c>
     </row>
@@ -6777,106 +9208,106 @@
           <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="63">
         <v>120</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="65">
         <v>41884</v>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="67">
         <v>2.86505586858944</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="62" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA BIOENERGÉTICA DEL NORTE DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="E15" s="47">
+      <c r="D15" s="62" t="inlineStr">
+        <is>
+          <t>PROVINCIA BIOENERGETICA DEL NORTE DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="E15" s="64">
         <v>1266</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="66">
         <v>175488</v>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="68">
         <v>7.21416849015317</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>NORTE</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="C16" s="62" t="inlineStr">
+        <is>
+          <t>NORTE</t>
+        </is>
+      </c>
+      <c r="D16" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E16" s="47">
+      <c r="E16" s="64">
         <v>1184</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="66">
         <v>255681</v>
       </c>
-      <c r="G16" s="51">
+      <c r="G16" s="68">
         <v>4.63077037402075</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="62" t="inlineStr">
         <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="62" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="64">
         <v>27352</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="66">
         <v>6821720</v>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="68">
         <v>4.00954597960632</v>
       </c>
     </row>
@@ -6892,47 +9323,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="70" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="70" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="70" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="70" t="inlineStr">
         <is>
           <t>Muy seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="70" t="inlineStr">
         <is>
           <t>Seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="70" t="inlineStr">
         <is>
           <t>Inseguro (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="70" t="inlineStr">
         <is>
           <t>Muy inseguro (%)</t>
         </is>
@@ -6949,19 +9380,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="56">
+      <c r="C2" s="75">
         <v>344</v>
       </c>
-      <c r="D2" s="52">
+      <c r="D2" s="71">
         <v>0.0675601418297848</v>
       </c>
-      <c r="E2" s="53">
+      <c r="E2" s="72">
         <v>0.685130309027178</v>
       </c>
-      <c r="F2" s="54">
+      <c r="F2" s="73">
         <v>0.198617934781808</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="74">
         <v>0.0486916143612287</v>
       </c>
     </row>
@@ -6976,19 +9407,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="56">
+      <c r="C3" s="75">
         <v>344</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="71">
         <v>0.136523652047281</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="72">
         <v>0.682440090821911</v>
       </c>
-      <c r="F3" s="54">
+      <c r="F3" s="73">
         <v>0.145725108854342</v>
       </c>
-      <c r="G3" s="55">
+      <c r="G3" s="74">
         <v>0.0353111482764656</v>
       </c>
     </row>
@@ -7003,19 +9434,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="56">
+      <c r="C4" s="75">
         <v>336</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="71">
         <v>0.0961090700618537</v>
       </c>
-      <c r="E4" s="53">
+      <c r="E4" s="72">
         <v>0.758001457119556</v>
       </c>
-      <c r="F4" s="54">
+      <c r="F4" s="73">
         <v>0.110291510742229</v>
       </c>
-      <c r="G4" s="55">
+      <c r="G4" s="74">
         <v>0.0355979620763621</v>
       </c>
     </row>
@@ -7030,19 +9461,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="75">
         <v>216</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="71">
         <v>0.0677601343323669</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="72">
         <v>0.745883146498697</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="73">
         <v>0.173250649134815</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="74">
         <v>0.0131060700341212</v>
       </c>
     </row>
@@ -7057,19 +9488,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="75">
         <v>272</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="71">
         <v>0.0707824065531934</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="72">
         <v>0.780361859680954</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="73">
         <v>0.141019611660632</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="74">
         <v>0.00783612210522076</v>
       </c>
     </row>
@@ -7084,19 +9515,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="75">
         <v>272</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="71">
         <v>0.121434107868613</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="72">
         <v>0.720848681945732</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="73">
         <v>0.12331756279583</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="74">
         <v>0.0343996473898254</v>
       </c>
     </row>
@@ -7111,19 +9542,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="75">
         <v>240</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="71">
         <v>0.0702898080427005</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="72">
         <v>0.774056105664931</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="73">
         <v>0.143702103045247</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="74">
         <v>0.0119519832471212</v>
       </c>
     </row>
@@ -7138,19 +9569,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="75">
         <v>249</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="71">
         <v>0.0700259516429931</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="72">
         <v>0.826434494997797</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="73">
         <v>0.0828698498366347</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="74">
         <v>0.0206697035225749</v>
       </c>
     </row>
@@ -7166,47 +9597,47 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="77" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="77" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="77" t="inlineStr">
         <is>
           <t>N respuestas</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="77" t="inlineStr">
         <is>
           <t>Más seguro (%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="77" t="inlineStr">
         <is>
           <t>Menos seguro (%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="77" t="inlineStr">
         <is>
           <t>Igual (%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="77" t="inlineStr">
         <is>
           <t>No sabe/No responde (%)</t>
         </is>
@@ -7223,19 +9654,19 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="C2" s="61">
+      <c r="C2" s="82">
         <v>344</v>
       </c>
-      <c r="D2" s="57">
+      <c r="D2" s="78">
         <v>0.169651549214151</v>
       </c>
-      <c r="E2" s="58">
+      <c r="E2" s="79">
         <v>0.144357208612453</v>
       </c>
-      <c r="F2" s="59">
+      <c r="F2" s="80">
         <v>0.642776137143313</v>
       </c>
-      <c r="G2" s="60">
+      <c r="G2" s="81">
         <v>0.0432151050300823</v>
       </c>
     </row>
@@ -7250,19 +9681,19 @@
           <t>2019 (1)</t>
         </is>
       </c>
-      <c r="C3" s="61">
+      <c r="C3" s="82">
         <v>344</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="78">
         <v>0.307946361051725</v>
       </c>
-      <c r="E3" s="58">
+      <c r="E3" s="79">
         <v>0.139008475941576</v>
       </c>
-      <c r="F3" s="59">
+      <c r="F3" s="80">
         <v>0.508254717198475</v>
       </c>
-      <c r="G3" s="60">
+      <c r="G3" s="81">
         <v>0.0447904458082242</v>
       </c>
     </row>
@@ -7277,19 +9708,19 @@
           <t>2019 (2)</t>
         </is>
       </c>
-      <c r="C4" s="61">
+      <c r="C4" s="82">
         <v>336</v>
       </c>
-      <c r="D4" s="57">
+      <c r="D4" s="78">
         <v>0.302259266762212</v>
       </c>
-      <c r="E4" s="58">
+      <c r="E4" s="79">
         <v>0.10751935468985</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="80">
         <v>0.585534319714311</v>
       </c>
-      <c r="G4" s="60">
+      <c r="G4" s="81">
         <v>0.00468705883362734</v>
       </c>
     </row>
@@ -7304,19 +9735,19 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="C5" s="61">
+      <c r="C5" s="82">
         <v>216</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="78">
         <v>0.185740072374087</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="79">
         <v>0.109941614677601</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="80">
         <v>0.701103863871695</v>
       </c>
-      <c r="G5" s="60">
+      <c r="G5" s="81">
         <v>0.00321444907661701</v>
       </c>
     </row>
@@ -7331,19 +9762,19 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="82">
         <v>272</v>
       </c>
-      <c r="D6" s="57">
+      <c r="D6" s="78">
         <v>0.147970751929919</v>
       </c>
-      <c r="E6" s="58">
+      <c r="E6" s="79">
         <v>0.0874874841976774</v>
       </c>
-      <c r="F6" s="59">
+      <c r="F6" s="80">
         <v>0.764541763872403</v>
       </c>
-      <c r="G6" s="60">
+      <c r="G6" s="81">
         <v>0</v>
       </c>
     </row>
@@ -7358,19 +9789,19 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="C7" s="61">
+      <c r="C7" s="82">
         <v>272</v>
       </c>
-      <c r="D7" s="57">
+      <c r="D7" s="78">
         <v>0.212443612741505</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="79">
         <v>0.0723293191309152</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="80">
         <v>0.714341170667201</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="81">
         <v>0.000885897460378978</v>
       </c>
     </row>
@@ -7385,19 +9816,19 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="82">
         <v>240</v>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="78">
         <v>0.195488724800149</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="79">
         <v>0.13960463879758</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="80">
         <v>0.657542123955844</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G8" s="81">
         <v>0.00736451244642682</v>
       </c>
     </row>
@@ -7412,19 +9843,19 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="82">
         <v>249</v>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="78">
         <v>0.210011321817851</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="79">
         <v>0.0699138762595573</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="80">
         <v>0.712957658408463</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="81">
         <v>0.00711714351412855</v>
       </c>
     </row>
